--- a/tools/importer/reports/import-catalog.report.xlsx
+++ b/tools/importer/reports/import-catalog.report.xlsx
@@ -73,7 +73,7 @@
     <t>toplevel</t>
   </si>
   <si>
-    <t>2026-09-09T06:27:59.044Z</t>
+    <t>2026-09-09T07:10:01.044Z</t>
   </si>
   <si>
     <t>Explore</t>
@@ -91,7 +91,7 @@
     <t>en-us/learn</t>
   </si>
   <si>
-    <t>2026-09-09T06:28:14.613Z</t>
+    <t>2026-09-09T07:10:17.544Z</t>
   </si>
   <si>
     <t>DS Academy: Flexible Dental Education for Professional Growth</t>
@@ -130,7 +130,7 @@
     <t>en-us/support</t>
   </si>
   <si>
-    <t>2026-09-09T06:28:44.655Z</t>
+    <t>2026-09-09T07:10:48.995Z</t>
   </si>
   <si>
     <t>Customer Support: FAQ's</t>
@@ -148,7 +148,7 @@
     <t>en-us/why-ds</t>
   </si>
   <si>
-    <t>2026-09-09T06:28:29.308Z</t>
+    <t>2026-09-09T07:10:32.703Z</t>
   </si>
   <si>
     <t>Why DS</t>
@@ -169,7 +169,7 @@
     <t>catalog</t>
   </si>
   <si>
-    <t>2026-09-09T06:39:35.908Z</t>
+    <t>2026-09-09T07:11:26.803Z</t>
   </si>
   <si>
     <t>Explore Digital Dentistry with Dentsply Sirona</t>
@@ -187,7 +187,7 @@
     <t>en-us/explore/endodontics</t>
   </si>
   <si>
-    <t>2026-09-09T06:40:39.837Z</t>
+    <t>2026-09-09T07:12:31.603Z</t>
   </si>
   <si>
     <t>Comprehensive Endodontic Solutions</t>
@@ -205,7 +205,7 @@
     <t>en-us/explore/implant-dentistry</t>
   </si>
   <si>
-    <t>2026-09-09T06:40:07.006Z</t>
+    <t>2026-09-09T07:11:57.712Z</t>
   </si>
   <si>
     <t>Dental Implant Systems: Discover now!</t>
@@ -223,7 +223,7 @@
     <t>en-us/explore/orthodontics</t>
   </si>
   <si>
-    <t>2026-09-09T07:08:05.907Z</t>
+    <t>2026-09-09T07:12:15.079Z</t>
   </si>
   <si>
     <t>Orthodontic Products &amp; Solutions</t>
@@ -241,7 +241,7 @@
     <t>en-us/explore/preventive</t>
   </si>
   <si>
-    <t>2026-09-09T06:40:56.604Z</t>
+    <t>2026-09-09T07:12:48.028Z</t>
   </si>
   <si>
     <t>Comprehensive preventive care solutions for healthier smiles</t>
@@ -259,7 +259,7 @@
     <t>en-us/explore/restorative</t>
   </si>
   <si>
-    <t>2026-09-09T06:39:51.237Z</t>
+    <t>2026-09-09T07:11:41.504Z</t>
   </si>
   <si>
     <t>Dental Restorative Products and more!</t>
@@ -277,7 +277,7 @@
     <t>en-us/support/help-topics</t>
   </si>
   <si>
-    <t>2026-09-09T06:43:48.366Z</t>
+    <t>2026-09-09T07:15:32.117Z</t>
   </si>
   <si>
     <t>Help Topics</t>
@@ -295,7 +295,7 @@
     <t>en-us/learn/education/continuing-education</t>
   </si>
   <si>
-    <t>2026-09-09T06:43:02.340Z</t>
+    <t>2026-09-09T07:14:46.659Z</t>
   </si>
   <si>
     <t>Dental Continuing Education with Courses &amp; Videos</t>
@@ -313,7 +313,7 @@
     <t>en-us/learn/education/practice-management-marketing</t>
   </si>
   <si>
-    <t>2026-09-09T06:43:20.270Z</t>
+    <t>2026-09-09T07:15:03.161Z</t>
   </si>
   <si>
     <t>Practice Management &amp; Marketing Course-Overview</t>
@@ -331,7 +331,7 @@
     <t>en-us/support/resources/download-center</t>
   </si>
   <si>
-    <t>2026-09-09T07:08:25.654Z</t>
+    <t>2026-09-09T07:15:48.977Z</t>
   </si>
   <si>
     <t>IFU, SDS, Instructions for Use &amp; Safety Data Sheets USA</t>
@@ -349,7 +349,7 @@
     <t>en-us/why-ds/our-programs/one-ds</t>
   </si>
   <si>
-    <t>2026-09-09T06:43:34.952Z</t>
+    <t>2026-09-09T07:15:17.827Z</t>
   </si>
   <si>
     <t>ONE DS Loyalty Program: Rewards for Dental Professionals</t>
@@ -367,7 +367,7 @@
     <t>en-us/explore/digital-dentistry/brands/ds-core</t>
   </si>
   <si>
-    <t>2026-09-09T06:41:14.763Z</t>
+    <t>2026-09-09T07:13:06.897Z</t>
   </si>
   <si>
     <t>Cloud Solution for Dentists: Clinical applications for streamlined dental workflows</t>
@@ -385,7 +385,7 @@
     <t>en-us/explore/digital-dentistry/brands/primescan-2</t>
   </si>
   <si>
-    <t>2026-09-09T06:41:33.970Z</t>
+    <t>2026-09-09T07:13:24.604Z</t>
   </si>
   <si>
     <t>Primescan 2</t>
@@ -403,7 +403,7 @@
     <t>en-us/explore/digital-dentistry/product-topics/digital-impression</t>
   </si>
   <si>
-    <t>2026-09-09T06:44:54.504Z</t>
+    <t>2026-09-09T07:16:40.705Z</t>
   </si>
   <si>
     <t>Intraoral Dental Scanners</t>
@@ -421,7 +421,7 @@
     <t>en-us/explore/endodontics/brands/waveone-gold</t>
   </si>
   <si>
-    <t>2026-09-09T06:41:51.412Z</t>
+    <t>2026-09-09T07:13:40.015Z</t>
   </si>
   <si>
     <t>WaveOne Gold: Simplified root canal shaping &amp; obturation</t>
@@ -439,7 +439,7 @@
     <t>en-us/explore/implant-dentistry/brands/astra-tech-implant-system-ev</t>
   </si>
   <si>
-    <t>2026-09-09T06:42:09.229Z</t>
+    <t>2026-09-09T07:13:58.098Z</t>
   </si>
   <si>
     <t>Astra Tech Implant System EV</t>
@@ -457,7 +457,7 @@
     <t>en-us/explore/implant-dentistry/product-topics/product-selection-guide</t>
   </si>
   <si>
-    <t>2026-09-09T06:44:37.605Z</t>
+    <t>2026-09-09T07:16:24.115Z</t>
   </si>
   <si>
     <t>Product Selection Guide USA</t>
@@ -475,7 +475,7 @@
     <t>en-us/explore/orthodontics/brands/suresmile-clear-aligner</t>
   </si>
   <si>
-    <t>2026-09-09T06:42:27.028Z</t>
+    <t>2026-09-09T07:14:14.353Z</t>
   </si>
   <si>
     <t>SureSmile Clear Aligner</t>
@@ -493,7 +493,7 @@
     <t>en-us/explore/preventive/brands/cavitron-300</t>
   </si>
   <si>
-    <t>2026-09-09T06:42:45.228Z</t>
+    <t>2026-09-09T07:14:30.639Z</t>
   </si>
   <si>
     <t>Cavitron® 300 Series</t>
@@ -511,7 +511,7 @@
     <t>en-us/explore/restorative/brands/tph-spectra</t>
   </si>
   <si>
-    <t>2026-09-09T06:44:24.030Z</t>
+    <t>2026-09-09T07:16:09.228Z</t>
   </si>
   <si>
     <t>TPH Spectra® ST Family</t>
